--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,6 +1694,471 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115116043</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8397</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>654885</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6565998</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>115118236</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79068</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>654901</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6565999</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115116034</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90283</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>654869</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6566029</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115118627</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79068</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>654819</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6566089</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2159,6 +2159,454 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>115137123</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8408</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>654884</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6566030</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115137071</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5165</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>654914</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6566062</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115131856</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90227</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>654898</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6566061</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>115137051</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5165</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>654898</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6566061</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -6680,7 +6680,7 @@
         <v>119576631</v>
       </c>
       <c r="B55" t="n">
-        <v>91842</v>
+        <v>91860</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -6906,10 +6906,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122128440</v>
+        <v>122129248</v>
       </c>
       <c r="B57" t="n">
-        <v>57390</v>
+        <v>90809</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6922,39 +6922,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654898</v>
+        <v>654831</v>
       </c>
       <c r="R57" t="n">
-        <v>6565826</v>
+        <v>6566094</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6981,12 +6976,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7013,10 +7018,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122129248</v>
+        <v>122128440</v>
       </c>
       <c r="B58" t="n">
-        <v>90799</v>
+        <v>57390</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7029,34 +7034,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654831</v>
+        <v>654898</v>
       </c>
       <c r="R58" t="n">
-        <v>6566094</v>
+        <v>6565826</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7083,22 +7093,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -6906,10 +6906,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122129248</v>
+        <v>122129293</v>
       </c>
       <c r="B57" t="n">
-        <v>90809</v>
+        <v>57390</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6922,34 +6922,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654831</v>
+        <v>654792</v>
       </c>
       <c r="R57" t="n">
-        <v>6566094</v>
+        <v>6566105</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6981,7 +6986,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6991,7 +6996,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7018,10 +7023,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122128440</v>
+        <v>122129248</v>
       </c>
       <c r="B58" t="n">
-        <v>57390</v>
+        <v>90809</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7034,39 +7039,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654898</v>
+        <v>654831</v>
       </c>
       <c r="R58" t="n">
-        <v>6565826</v>
+        <v>6566094</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7093,12 +7093,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7125,7 +7135,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122129293</v>
+        <v>122128440</v>
       </c>
       <c r="B59" t="n">
         <v>57390</v>
@@ -7166,14 +7176,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654792</v>
+        <v>654898</v>
       </c>
       <c r="R59" t="n">
-        <v>6566105</v>
+        <v>6565826</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7200,22 +7210,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -6906,10 +6906,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122129293</v>
+        <v>122128440</v>
       </c>
       <c r="B57" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6947,14 +6947,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654792</v>
+        <v>654898</v>
       </c>
       <c r="R57" t="n">
-        <v>6566105</v>
+        <v>6565826</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6981,22 +6981,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7026,7 +7016,7 @@
         <v>122129248</v>
       </c>
       <c r="B58" t="n">
-        <v>90809</v>
+        <v>90821</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7135,10 +7125,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122128440</v>
+        <v>122129293</v>
       </c>
       <c r="B59" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7176,14 +7166,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654898</v>
+        <v>654792</v>
       </c>
       <c r="R59" t="n">
-        <v>6565826</v>
+        <v>6566105</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7210,12 +7200,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -6906,7 +6906,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122128440</v>
+        <v>122129293</v>
       </c>
       <c r="B57" t="n">
         <v>57395</v>
@@ -6947,14 +6947,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654898</v>
+        <v>654792</v>
       </c>
       <c r="R57" t="n">
-        <v>6565826</v>
+        <v>6566105</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6981,12 +6981,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7013,10 +7023,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122129248</v>
+        <v>122128440</v>
       </c>
       <c r="B58" t="n">
-        <v>90821</v>
+        <v>57395</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7029,34 +7039,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654831</v>
+        <v>654898</v>
       </c>
       <c r="R58" t="n">
-        <v>6566094</v>
+        <v>6565826</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7083,22 +7098,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7125,10 +7130,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122129293</v>
+        <v>122129248</v>
       </c>
       <c r="B59" t="n">
-        <v>57395</v>
+        <v>90828</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7141,39 +7146,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654792</v>
+        <v>654831</v>
       </c>
       <c r="R59" t="n">
-        <v>6566105</v>
+        <v>6566094</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -6924,11 +6924,6 @@
       <c r="E57" t="n">
         <v>100049</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -7023,10 +7018,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122128440</v>
+        <v>122129248</v>
       </c>
       <c r="B58" t="n">
-        <v>57395</v>
+        <v>90833</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7039,39 +7034,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654898</v>
+        <v>654831</v>
       </c>
       <c r="R58" t="n">
-        <v>6565826</v>
+        <v>6566094</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7098,12 +7083,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7130,10 +7125,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122129248</v>
+        <v>122128440</v>
       </c>
       <c r="B59" t="n">
-        <v>90828</v>
+        <v>57395</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7146,34 +7141,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654831</v>
+        <v>654898</v>
       </c>
       <c r="R59" t="n">
-        <v>6566094</v>
+        <v>6565826</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7200,22 +7195,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -6906,10 +6906,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122129293</v>
+        <v>122129248</v>
       </c>
       <c r="B57" t="n">
-        <v>57395</v>
+        <v>90846</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6922,34 +6922,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>5442</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654792</v>
+        <v>654831</v>
       </c>
       <c r="R57" t="n">
-        <v>6566105</v>
+        <v>6566094</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7018,10 +7018,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122129248</v>
+        <v>122128440</v>
       </c>
       <c r="B58" t="n">
-        <v>90833</v>
+        <v>57399</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7034,29 +7034,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>100049</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654831</v>
+        <v>654898</v>
       </c>
       <c r="R58" t="n">
-        <v>6566094</v>
+        <v>6565826</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7083,22 +7093,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7125,10 +7125,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122128440</v>
+        <v>122129293</v>
       </c>
       <c r="B59" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7143,6 +7143,11 @@
       <c r="E59" t="n">
         <v>100049</v>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -7161,14 +7166,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654898</v>
+        <v>654792</v>
       </c>
       <c r="R59" t="n">
-        <v>6565826</v>
+        <v>6566105</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7195,12 +7200,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -6909,7 +6909,7 @@
         <v>122129248</v>
       </c>
       <c r="B57" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7354,10 +7354,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122765368</v>
+        <v>122765657</v>
       </c>
       <c r="B61" t="n">
-        <v>5173</v>
+        <v>90964</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7366,25 +7366,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654946</v>
+        <v>654811</v>
       </c>
       <c r="R61" t="n">
-        <v>6566044</v>
+        <v>6566078</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7466,10 +7466,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122765355</v>
+        <v>122765368</v>
       </c>
       <c r="B62" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7478,43 +7478,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654953</v>
+        <v>654946</v>
       </c>
       <c r="R62" t="n">
-        <v>6566038</v>
+        <v>6566044</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7546,7 +7541,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7556,7 +7551,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7583,10 +7578,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122765305</v>
+        <v>122765355</v>
       </c>
       <c r="B63" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7595,38 +7590,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654978</v>
+        <v>654953</v>
       </c>
       <c r="R63" t="n">
-        <v>6565979</v>
+        <v>6566038</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7695,10 +7695,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122765657</v>
+        <v>122765305</v>
       </c>
       <c r="B64" t="n">
-        <v>90960</v>
+        <v>5173</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7707,25 +7707,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654811</v>
+        <v>654978</v>
       </c>
       <c r="R64" t="n">
-        <v>6566078</v>
+        <v>6565979</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7807,14 +7807,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122765519</v>
+        <v>122788386</v>
       </c>
       <c r="B65" t="n">
-        <v>94748</v>
+        <v>97309</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7823,21 +7823,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2809</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654844</v>
+        <v>654629</v>
       </c>
       <c r="R65" t="n">
-        <v>6566122</v>
+        <v>6566054</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7877,22 +7877,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7919,10 +7919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122788085</v>
+        <v>122788048</v>
       </c>
       <c r="B66" t="n">
-        <v>95118</v>
+        <v>92225</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7935,34 +7935,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654853</v>
+        <v>654899</v>
       </c>
       <c r="R66" t="n">
-        <v>6565997</v>
+        <v>6565949</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8031,10 +8031,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122788386</v>
+        <v>122788791</v>
       </c>
       <c r="B67" t="n">
-        <v>97301</v>
+        <v>57369</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8043,38 +8043,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>100001</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654629</v>
+        <v>654687</v>
       </c>
       <c r="R67" t="n">
-        <v>6566054</v>
+        <v>6566048</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8106,7 +8111,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8116,7 +8121,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8143,55 +8148,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122788791</v>
+        <v>122765519</v>
       </c>
       <c r="B68" t="n">
-        <v>57369</v>
+        <v>94756</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100001</v>
+        <v>2809</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654687</v>
+        <v>654844</v>
       </c>
       <c r="R68" t="n">
-        <v>6566048</v>
+        <v>6566122</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8218,22 +8218,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8260,10 +8260,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122788048</v>
+        <v>122788085</v>
       </c>
       <c r="B69" t="n">
-        <v>92221</v>
+        <v>95126</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8276,34 +8276,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654899</v>
+        <v>654853</v>
       </c>
       <c r="R69" t="n">
-        <v>6565949</v>
+        <v>6565997</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7466,10 +7466,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122765368</v>
+        <v>122765355</v>
       </c>
       <c r="B62" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7478,38 +7478,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654946</v>
+        <v>654953</v>
       </c>
       <c r="R62" t="n">
-        <v>6566044</v>
+        <v>6566038</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7541,7 +7546,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7551,7 +7556,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7578,10 +7583,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122765355</v>
+        <v>122765305</v>
       </c>
       <c r="B63" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7590,43 +7595,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654953</v>
+        <v>654978</v>
       </c>
       <c r="R63" t="n">
-        <v>6566038</v>
+        <v>6565979</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7695,7 +7695,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122765305</v>
+        <v>122765368</v>
       </c>
       <c r="B64" t="n">
         <v>5173</v>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654978</v>
+        <v>654946</v>
       </c>
       <c r="R64" t="n">
-        <v>6565979</v>
+        <v>6566044</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8031,10 +8031,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122788791</v>
+        <v>122788085</v>
       </c>
       <c r="B67" t="n">
-        <v>57369</v>
+        <v>95126</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8043,43 +8043,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100001</v>
+        <v>2180</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654687</v>
+        <v>654853</v>
       </c>
       <c r="R67" t="n">
-        <v>6566048</v>
+        <v>6565997</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8111,7 +8106,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8121,7 +8116,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8148,50 +8143,55 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122765519</v>
+        <v>122788791</v>
       </c>
       <c r="B68" t="n">
-        <v>94756</v>
+        <v>57369</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2809</v>
+        <v>100001</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654844</v>
+        <v>654687</v>
       </c>
       <c r="R68" t="n">
-        <v>6566122</v>
+        <v>6566048</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8218,22 +8218,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8260,14 +8260,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122788085</v>
+        <v>122765519</v>
       </c>
       <c r="B69" t="n">
-        <v>95126</v>
+        <v>94756</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8276,21 +8276,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2180</v>
+        <v>2809</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654853</v>
+        <v>654844</v>
       </c>
       <c r="R69" t="n">
-        <v>6565997</v>
+        <v>6566122</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8330,22 +8330,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7354,10 +7354,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122765657</v>
+        <v>122765368</v>
       </c>
       <c r="B61" t="n">
-        <v>90964</v>
+        <v>5173</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7366,25 +7366,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654811</v>
+        <v>654946</v>
       </c>
       <c r="R61" t="n">
-        <v>6566078</v>
+        <v>6566044</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7466,10 +7466,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122765355</v>
+        <v>122765305</v>
       </c>
       <c r="B62" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7478,43 +7478,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654953</v>
+        <v>654978</v>
       </c>
       <c r="R62" t="n">
-        <v>6566038</v>
+        <v>6565979</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7546,7 +7541,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7556,7 +7551,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7583,10 +7578,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122765305</v>
+        <v>122765657</v>
       </c>
       <c r="B63" t="n">
-        <v>5173</v>
+        <v>90964</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7595,25 +7590,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7623,10 +7618,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654978</v>
+        <v>654811</v>
       </c>
       <c r="R63" t="n">
-        <v>6565979</v>
+        <v>6566078</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7658,7 +7653,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7668,7 +7663,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7695,10 +7690,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122765368</v>
+        <v>122765355</v>
       </c>
       <c r="B64" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7707,38 +7702,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654946</v>
+        <v>654953</v>
       </c>
       <c r="R64" t="n">
-        <v>6566044</v>
+        <v>6566038</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7807,10 +7807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122788386</v>
+        <v>122788791</v>
       </c>
       <c r="B65" t="n">
-        <v>97309</v>
+        <v>57369</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7819,38 +7819,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>100001</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654629</v>
+        <v>654687</v>
       </c>
       <c r="R65" t="n">
-        <v>6566054</v>
+        <v>6566048</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7882,7 +7887,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7892,7 +7897,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7919,14 +7924,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122788048</v>
+        <v>122765519</v>
       </c>
       <c r="B66" t="n">
-        <v>92225</v>
+        <v>94758</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7935,34 +7940,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>2809</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654899</v>
+        <v>654844</v>
       </c>
       <c r="R66" t="n">
-        <v>6565949</v>
+        <v>6566122</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7989,22 +7994,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8031,10 +8036,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122788085</v>
+        <v>122788386</v>
       </c>
       <c r="B67" t="n">
-        <v>95126</v>
+        <v>97311</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8047,21 +8052,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8071,10 +8076,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654853</v>
+        <v>654629</v>
       </c>
       <c r="R67" t="n">
-        <v>6565997</v>
+        <v>6566054</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8106,7 +8111,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8116,7 +8121,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8143,10 +8148,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122788791</v>
+        <v>122788085</v>
       </c>
       <c r="B68" t="n">
-        <v>57369</v>
+        <v>95128</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8155,43 +8160,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100001</v>
+        <v>2180</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654687</v>
+        <v>654853</v>
       </c>
       <c r="R68" t="n">
-        <v>6566048</v>
+        <v>6565997</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8260,14 +8260,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122765519</v>
+        <v>122788048</v>
       </c>
       <c r="B69" t="n">
-        <v>94756</v>
+        <v>92225</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8276,34 +8276,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2809</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654844</v>
+        <v>654899</v>
       </c>
       <c r="R69" t="n">
-        <v>6566122</v>
+        <v>6565949</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8330,22 +8330,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7354,7 +7354,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122765368</v>
+        <v>122765305</v>
       </c>
       <c r="B61" t="n">
         <v>5173</v>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654946</v>
+        <v>654978</v>
       </c>
       <c r="R61" t="n">
-        <v>6566044</v>
+        <v>6565979</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7466,10 +7466,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122765305</v>
+        <v>122765355</v>
       </c>
       <c r="B62" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7478,38 +7478,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654978</v>
+        <v>654953</v>
       </c>
       <c r="R62" t="n">
-        <v>6565979</v>
+        <v>6566038</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7541,7 +7546,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7551,7 +7556,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7690,10 +7695,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122765355</v>
+        <v>122765368</v>
       </c>
       <c r="B64" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7702,43 +7707,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654953</v>
+        <v>654946</v>
       </c>
       <c r="R64" t="n">
-        <v>6566038</v>
+        <v>6566044</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7924,14 +7924,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122765519</v>
+        <v>122788048</v>
       </c>
       <c r="B66" t="n">
-        <v>94758</v>
+        <v>92225</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7940,34 +7940,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2809</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654844</v>
+        <v>654899</v>
       </c>
       <c r="R66" t="n">
-        <v>6566122</v>
+        <v>6565949</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7994,22 +7994,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8148,14 +8148,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122788085</v>
+        <v>122765519</v>
       </c>
       <c r="B68" t="n">
-        <v>95128</v>
+        <v>94758</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8164,21 +8164,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2180</v>
+        <v>2809</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654853</v>
+        <v>654844</v>
       </c>
       <c r="R68" t="n">
-        <v>6565997</v>
+        <v>6566122</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8218,22 +8218,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8260,10 +8260,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122788048</v>
+        <v>122788085</v>
       </c>
       <c r="B69" t="n">
-        <v>92225</v>
+        <v>95128</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8276,34 +8276,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654899</v>
+        <v>654853</v>
       </c>
       <c r="R69" t="n">
-        <v>6565949</v>
+        <v>6565997</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7466,10 +7466,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122765355</v>
+        <v>122765368</v>
       </c>
       <c r="B62" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7478,43 +7478,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654953</v>
+        <v>654946</v>
       </c>
       <c r="R62" t="n">
-        <v>6566038</v>
+        <v>6566044</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7546,7 +7541,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7556,7 +7551,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7586,7 +7581,7 @@
         <v>122765657</v>
       </c>
       <c r="B63" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7695,10 +7690,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122765368</v>
+        <v>122765355</v>
       </c>
       <c r="B64" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7707,38 +7702,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654946</v>
+        <v>654953</v>
       </c>
       <c r="R64" t="n">
-        <v>6566044</v>
+        <v>6566038</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7807,10 +7807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122788791</v>
+        <v>122788085</v>
       </c>
       <c r="B65" t="n">
-        <v>57369</v>
+        <v>95136</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7819,43 +7819,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100001</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654687</v>
+        <v>654853</v>
       </c>
       <c r="R65" t="n">
-        <v>6566048</v>
+        <v>6565997</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7887,7 +7882,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7897,7 +7892,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7924,10 +7919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122788048</v>
+        <v>122788386</v>
       </c>
       <c r="B66" t="n">
-        <v>92225</v>
+        <v>97319</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7940,34 +7935,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654899</v>
+        <v>654629</v>
       </c>
       <c r="R66" t="n">
-        <v>6565949</v>
+        <v>6566054</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7999,7 +7994,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8009,7 +8004,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8036,14 +8031,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122788386</v>
+        <v>122765519</v>
       </c>
       <c r="B67" t="n">
-        <v>97311</v>
+        <v>94766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8052,21 +8047,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>2809</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8076,10 +8071,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654629</v>
+        <v>654844</v>
       </c>
       <c r="R67" t="n">
-        <v>6566054</v>
+        <v>6566122</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8106,22 +8101,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8148,14 +8143,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122765519</v>
+        <v>122788048</v>
       </c>
       <c r="B68" t="n">
-        <v>94758</v>
+        <v>92233</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8164,34 +8159,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2809</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654844</v>
+        <v>654899</v>
       </c>
       <c r="R68" t="n">
-        <v>6566122</v>
+        <v>6565949</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8218,22 +8213,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8260,10 +8255,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122788085</v>
+        <v>122788791</v>
       </c>
       <c r="B69" t="n">
-        <v>95128</v>
+        <v>57369</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8272,38 +8267,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2180</v>
+        <v>100001</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654853</v>
+        <v>654687</v>
       </c>
       <c r="R69" t="n">
-        <v>6565997</v>
+        <v>6566048</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7354,10 +7354,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122765305</v>
+        <v>122765355</v>
       </c>
       <c r="B61" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7366,38 +7366,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654978</v>
+        <v>654953</v>
       </c>
       <c r="R61" t="n">
-        <v>6565979</v>
+        <v>6566038</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7429,7 +7434,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7439,7 +7444,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7690,10 +7695,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122765355</v>
+        <v>122765305</v>
       </c>
       <c r="B64" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7702,43 +7707,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654953</v>
+        <v>654978</v>
       </c>
       <c r="R64" t="n">
-        <v>6566038</v>
+        <v>6565979</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7807,10 +7807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122788085</v>
+        <v>122788048</v>
       </c>
       <c r="B65" t="n">
-        <v>95136</v>
+        <v>92233</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7823,34 +7823,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654853</v>
+        <v>654899</v>
       </c>
       <c r="R65" t="n">
-        <v>6565997</v>
+        <v>6565949</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7919,10 +7919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122788386</v>
+        <v>122788085</v>
       </c>
       <c r="B66" t="n">
-        <v>97319</v>
+        <v>95136</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7935,21 +7935,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654629</v>
+        <v>654853</v>
       </c>
       <c r="R66" t="n">
-        <v>6566054</v>
+        <v>6565997</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8031,50 +8031,55 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122765519</v>
+        <v>122788791</v>
       </c>
       <c r="B67" t="n">
-        <v>94766</v>
+        <v>57369</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2809</v>
+        <v>100001</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654844</v>
+        <v>654687</v>
       </c>
       <c r="R67" t="n">
-        <v>6566122</v>
+        <v>6566048</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8101,22 +8106,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8143,10 +8148,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122788048</v>
+        <v>122788386</v>
       </c>
       <c r="B68" t="n">
-        <v>92233</v>
+        <v>97319</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8159,34 +8164,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654899</v>
+        <v>654629</v>
       </c>
       <c r="R68" t="n">
-        <v>6565949</v>
+        <v>6566054</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8218,7 +8223,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8228,7 +8233,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8255,55 +8260,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122788791</v>
+        <v>122765519</v>
       </c>
       <c r="B69" t="n">
-        <v>57369</v>
+        <v>94766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100001</v>
+        <v>2809</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654687</v>
+        <v>654844</v>
       </c>
       <c r="R69" t="n">
-        <v>6566048</v>
+        <v>6566122</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8330,22 +8330,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7919,10 +7919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122788085</v>
+        <v>122788386</v>
       </c>
       <c r="B66" t="n">
-        <v>95136</v>
+        <v>97319</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7935,21 +7935,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654853</v>
+        <v>654629</v>
       </c>
       <c r="R66" t="n">
-        <v>6565997</v>
+        <v>6566054</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8031,10 +8031,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122788791</v>
+        <v>122788085</v>
       </c>
       <c r="B67" t="n">
-        <v>57369</v>
+        <v>95136</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8043,43 +8043,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100001</v>
+        <v>2180</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654687</v>
+        <v>654853</v>
       </c>
       <c r="R67" t="n">
-        <v>6566048</v>
+        <v>6565997</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8111,7 +8106,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8121,7 +8116,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8148,10 +8143,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122788386</v>
+        <v>122788791</v>
       </c>
       <c r="B68" t="n">
-        <v>97319</v>
+        <v>57369</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8160,38 +8155,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>100001</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654629</v>
+        <v>654687</v>
       </c>
       <c r="R68" t="n">
-        <v>6566054</v>
+        <v>6566048</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7919,10 +7919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122788386</v>
+        <v>122788085</v>
       </c>
       <c r="B66" t="n">
-        <v>97319</v>
+        <v>95136</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7935,21 +7935,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654629</v>
+        <v>654853</v>
       </c>
       <c r="R66" t="n">
-        <v>6566054</v>
+        <v>6565997</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8031,10 +8031,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122788085</v>
+        <v>122788791</v>
       </c>
       <c r="B67" t="n">
-        <v>95136</v>
+        <v>57369</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8043,38 +8043,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2180</v>
+        <v>100001</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654853</v>
+        <v>654687</v>
       </c>
       <c r="R67" t="n">
-        <v>6565997</v>
+        <v>6566048</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8106,7 +8111,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8116,7 +8121,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8143,10 +8148,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122788791</v>
+        <v>122788386</v>
       </c>
       <c r="B68" t="n">
-        <v>57369</v>
+        <v>97319</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8155,43 +8160,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100001</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654687</v>
+        <v>654629</v>
       </c>
       <c r="R68" t="n">
-        <v>6566048</v>
+        <v>6566054</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7354,10 +7354,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122765355</v>
+        <v>122765368</v>
       </c>
       <c r="B61" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7366,43 +7366,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654953</v>
+        <v>654946</v>
       </c>
       <c r="R61" t="n">
-        <v>6566038</v>
+        <v>6566044</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7434,7 +7429,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7444,7 +7439,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7471,10 +7466,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122765368</v>
+        <v>122765355</v>
       </c>
       <c r="B62" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7483,38 +7478,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654946</v>
+        <v>654953</v>
       </c>
       <c r="R62" t="n">
-        <v>6566044</v>
+        <v>6566038</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7807,10 +7807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122788048</v>
+        <v>122788386</v>
       </c>
       <c r="B65" t="n">
-        <v>92233</v>
+        <v>97319</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7823,34 +7823,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654899</v>
+        <v>654629</v>
       </c>
       <c r="R65" t="n">
-        <v>6565949</v>
+        <v>6566054</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7919,10 +7919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122788085</v>
+        <v>122788048</v>
       </c>
       <c r="B66" t="n">
-        <v>95136</v>
+        <v>92233</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7935,34 +7935,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654853</v>
+        <v>654899</v>
       </c>
       <c r="R66" t="n">
-        <v>6565997</v>
+        <v>6565949</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8031,55 +8031,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122788791</v>
+        <v>122765519</v>
       </c>
       <c r="B67" t="n">
-        <v>57369</v>
+        <v>94766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100001</v>
+        <v>2809</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654687</v>
+        <v>654844</v>
       </c>
       <c r="R67" t="n">
-        <v>6566048</v>
+        <v>6566122</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8106,22 +8101,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8148,10 +8143,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122788386</v>
+        <v>122788791</v>
       </c>
       <c r="B68" t="n">
-        <v>97319</v>
+        <v>57369</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8160,38 +8155,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>100001</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654629</v>
+        <v>654687</v>
       </c>
       <c r="R68" t="n">
-        <v>6566054</v>
+        <v>6566048</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8260,14 +8260,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122765519</v>
+        <v>122788085</v>
       </c>
       <c r="B69" t="n">
-        <v>94766</v>
+        <v>95136</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8276,21 +8276,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2809</v>
+        <v>2180</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654844</v>
+        <v>654853</v>
       </c>
       <c r="R69" t="n">
-        <v>6566122</v>
+        <v>6565997</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8330,22 +8330,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7466,10 +7466,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122765355</v>
+        <v>122765657</v>
       </c>
       <c r="B62" t="n">
-        <v>57494</v>
+        <v>90972</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7482,39 +7482,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654953</v>
+        <v>654811</v>
       </c>
       <c r="R62" t="n">
-        <v>6566038</v>
+        <v>6566078</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7546,7 +7541,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7556,7 +7551,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7583,10 +7578,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122765657</v>
+        <v>122765355</v>
       </c>
       <c r="B63" t="n">
-        <v>90972</v>
+        <v>57494</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7599,34 +7594,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654811</v>
+        <v>654953</v>
       </c>
       <c r="R63" t="n">
-        <v>6566078</v>
+        <v>6566038</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7807,14 +7807,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122788386</v>
+        <v>122765519</v>
       </c>
       <c r="B65" t="n">
-        <v>97319</v>
+        <v>94766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7823,21 +7823,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>2809</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654629</v>
+        <v>654844</v>
       </c>
       <c r="R65" t="n">
-        <v>6566054</v>
+        <v>6566122</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7877,22 +7877,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7919,10 +7919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122788048</v>
+        <v>122788791</v>
       </c>
       <c r="B66" t="n">
-        <v>92233</v>
+        <v>57369</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7931,38 +7931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>100001</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654899</v>
+        <v>654687</v>
       </c>
       <c r="R66" t="n">
-        <v>6565949</v>
+        <v>6566048</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7994,7 +7999,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8004,7 +8009,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8031,14 +8036,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122765519</v>
+        <v>122788048</v>
       </c>
       <c r="B67" t="n">
-        <v>94766</v>
+        <v>92233</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8047,34 +8052,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2809</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654844</v>
+        <v>654899</v>
       </c>
       <c r="R67" t="n">
-        <v>6566122</v>
+        <v>6565949</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8101,22 +8106,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8143,10 +8148,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122788791</v>
+        <v>122788386</v>
       </c>
       <c r="B68" t="n">
-        <v>57369</v>
+        <v>97319</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8155,43 +8160,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100001</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654687</v>
+        <v>654629</v>
       </c>
       <c r="R68" t="n">
-        <v>6566048</v>
+        <v>6566054</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8370,6 +8370,123 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>123297960</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Ersboda , Rönninge, Srm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>655037</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6565990</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8487,6 +8487,246 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>123402528</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Ersboda naturskog, Srm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>654999</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6566083</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Martin Resare</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Martin Resare</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>123402533</v>
+      </c>
+      <c r="B72" t="n">
+        <v>58156</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Ersboda naturskog, Srm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>654999</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6566083</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Martin Resare</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Martin Resare</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7245,7 +7245,7 @@
         <v>122734105</v>
       </c>
       <c r="B60" t="n">
-        <v>43822</v>
+        <v>43825</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122765368</v>
+        <v>122765305</v>
       </c>
       <c r="B61" t="n">
         <v>5173</v>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654946</v>
+        <v>654978</v>
       </c>
       <c r="R61" t="n">
-        <v>6566044</v>
+        <v>6565979</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7466,10 +7466,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122765657</v>
+        <v>122765368</v>
       </c>
       <c r="B62" t="n">
-        <v>90972</v>
+        <v>5173</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7478,25 +7478,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7506,10 +7506,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654811</v>
+        <v>654946</v>
       </c>
       <c r="R62" t="n">
-        <v>6566078</v>
+        <v>6566044</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7581,7 +7581,7 @@
         <v>122765355</v>
       </c>
       <c r="B63" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7695,10 +7695,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122765305</v>
+        <v>122765657</v>
       </c>
       <c r="B64" t="n">
-        <v>5173</v>
+        <v>90975</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7707,25 +7707,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654978</v>
+        <v>654811</v>
       </c>
       <c r="R64" t="n">
-        <v>6565979</v>
+        <v>6566078</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7807,14 +7807,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122765519</v>
+        <v>122788085</v>
       </c>
       <c r="B65" t="n">
-        <v>94766</v>
+        <v>95139</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7823,21 +7823,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2809</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654844</v>
+        <v>654853</v>
       </c>
       <c r="R65" t="n">
-        <v>6566122</v>
+        <v>6565997</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7877,22 +7877,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7919,10 +7919,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122788791</v>
+        <v>122788386</v>
       </c>
       <c r="B66" t="n">
-        <v>57369</v>
+        <v>97322</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7931,43 +7931,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100001</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654687</v>
+        <v>654629</v>
       </c>
       <c r="R66" t="n">
-        <v>6566048</v>
+        <v>6566054</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7999,7 +7994,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8009,7 +8004,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8036,10 +8031,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122788048</v>
+        <v>122788791</v>
       </c>
       <c r="B67" t="n">
-        <v>92233</v>
+        <v>57372</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8048,38 +8043,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>100001</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654899</v>
+        <v>654687</v>
       </c>
       <c r="R67" t="n">
-        <v>6565949</v>
+        <v>6566048</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8148,10 +8148,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122788386</v>
+        <v>122788048</v>
       </c>
       <c r="B68" t="n">
-        <v>97319</v>
+        <v>92236</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8164,34 +8164,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654629</v>
+        <v>654899</v>
       </c>
       <c r="R68" t="n">
-        <v>6566054</v>
+        <v>6565949</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8260,14 +8260,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122788085</v>
+        <v>122765519</v>
       </c>
       <c r="B69" t="n">
-        <v>95136</v>
+        <v>94769</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8276,21 +8276,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2180</v>
+        <v>2809</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654853</v>
+        <v>654844</v>
       </c>
       <c r="R69" t="n">
-        <v>6565997</v>
+        <v>6566122</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8330,22 +8330,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8375,7 +8375,7 @@
         <v>123297960</v>
       </c>
       <c r="B70" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>123402528</v>
       </c>
       <c r="B71" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>123402533</v>
       </c>
       <c r="B72" t="n">
-        <v>58156</v>
+        <v>58159</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7698,7 +7698,7 @@
         <v>122765657</v>
       </c>
       <c r="B64" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7807,10 +7807,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122788085</v>
+        <v>122788386</v>
       </c>
       <c r="B65" t="n">
-        <v>95139</v>
+        <v>97324</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7823,21 +7823,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654853</v>
+        <v>654629</v>
       </c>
       <c r="R65" t="n">
-        <v>6565997</v>
+        <v>6566054</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7919,14 +7919,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122788386</v>
+        <v>122765519</v>
       </c>
       <c r="B66" t="n">
-        <v>97322</v>
+        <v>94771</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7935,21 +7935,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>2809</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654629</v>
+        <v>654844</v>
       </c>
       <c r="R66" t="n">
-        <v>6566054</v>
+        <v>6566122</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7989,22 +7989,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8148,10 +8148,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122788048</v>
+        <v>122788085</v>
       </c>
       <c r="B68" t="n">
-        <v>92236</v>
+        <v>95141</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8164,34 +8164,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654899</v>
+        <v>654853</v>
       </c>
       <c r="R68" t="n">
-        <v>6565949</v>
+        <v>6565997</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8260,14 +8260,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122765519</v>
+        <v>122788048</v>
       </c>
       <c r="B69" t="n">
-        <v>94769</v>
+        <v>92238</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8276,34 +8276,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2809</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654844</v>
+        <v>654899</v>
       </c>
       <c r="R69" t="n">
-        <v>6566122</v>
+        <v>6565949</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8330,22 +8330,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8489,10 +8489,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123402528</v>
+        <v>123402533</v>
       </c>
       <c r="B71" t="n">
-        <v>57851</v>
+        <v>58159</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8505,16 +8505,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8609,10 +8609,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123402533</v>
+        <v>123402528</v>
       </c>
       <c r="B72" t="n">
-        <v>58159</v>
+        <v>57851</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8625,16 +8625,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7354,10 +7354,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122765305</v>
+        <v>122765657</v>
       </c>
       <c r="B61" t="n">
-        <v>5173</v>
+        <v>90983</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7366,25 +7366,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654978</v>
+        <v>654811</v>
       </c>
       <c r="R61" t="n">
-        <v>6565979</v>
+        <v>6566078</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7466,7 +7466,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122765368</v>
+        <v>122765305</v>
       </c>
       <c r="B62" t="n">
         <v>5173</v>
@@ -7506,10 +7506,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654946</v>
+        <v>654978</v>
       </c>
       <c r="R62" t="n">
-        <v>6566044</v>
+        <v>6565979</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7578,10 +7578,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122765355</v>
+        <v>122765368</v>
       </c>
       <c r="B63" t="n">
-        <v>57497</v>
+        <v>5173</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7590,43 +7590,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654953</v>
+        <v>654946</v>
       </c>
       <c r="R63" t="n">
-        <v>6566038</v>
+        <v>6566044</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7658,7 +7653,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7668,7 +7663,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7695,10 +7690,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122765657</v>
+        <v>122765355</v>
       </c>
       <c r="B64" t="n">
-        <v>90977</v>
+        <v>57497</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7711,34 +7706,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654811</v>
+        <v>654953</v>
       </c>
       <c r="R64" t="n">
-        <v>6566078</v>
+        <v>6566038</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7810,7 +7810,7 @@
         <v>122788386</v>
       </c>
       <c r="B65" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7919,14 +7919,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122765519</v>
+        <v>122788048</v>
       </c>
       <c r="B66" t="n">
-        <v>94771</v>
+        <v>92244</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7935,34 +7935,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2809</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654844</v>
+        <v>654899</v>
       </c>
       <c r="R66" t="n">
-        <v>6566122</v>
+        <v>6565949</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7989,22 +7989,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8148,14 +8148,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122788085</v>
+        <v>122765519</v>
       </c>
       <c r="B68" t="n">
-        <v>95141</v>
+        <v>94777</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8164,21 +8164,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2180</v>
+        <v>2809</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654853</v>
+        <v>654844</v>
       </c>
       <c r="R68" t="n">
-        <v>6565997</v>
+        <v>6566122</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8218,22 +8218,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8260,10 +8260,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122788048</v>
+        <v>122788085</v>
       </c>
       <c r="B69" t="n">
-        <v>92238</v>
+        <v>95147</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8276,34 +8276,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654899</v>
+        <v>654853</v>
       </c>
       <c r="R69" t="n">
-        <v>6565949</v>
+        <v>6565997</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8489,10 +8489,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123402533</v>
+        <v>123402528</v>
       </c>
       <c r="B71" t="n">
-        <v>58159</v>
+        <v>57851</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8505,16 +8505,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8609,10 +8609,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123402528</v>
+        <v>123402533</v>
       </c>
       <c r="B72" t="n">
-        <v>57851</v>
+        <v>58159</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8625,16 +8625,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -7810,7 +7810,7 @@
         <v>122788386</v>
       </c>
       <c r="B65" t="n">
-        <v>97330</v>
+        <v>97333</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>122788048</v>
       </c>
       <c r="B66" t="n">
-        <v>92244</v>
+        <v>92247</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>122765519</v>
       </c>
       <c r="B68" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>122788085</v>
       </c>
       <c r="B69" t="n">
-        <v>95147</v>
+        <v>95150</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -8375,7 +8375,7 @@
         <v>123297960</v>
       </c>
       <c r="B70" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8489,10 +8489,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123402528</v>
+        <v>123402533</v>
       </c>
       <c r="B71" t="n">
-        <v>57851</v>
+        <v>58165</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8505,16 +8505,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8609,10 +8609,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123402533</v>
+        <v>123402528</v>
       </c>
       <c r="B72" t="n">
-        <v>58159</v>
+        <v>57857</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8625,16 +8625,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -8375,7 +8375,7 @@
         <v>123297960</v>
       </c>
       <c r="B70" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>123402533</v>
       </c>
       <c r="B71" t="n">
-        <v>58165</v>
+        <v>58168</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>123402528</v>
       </c>
       <c r="B72" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -8375,7 +8375,7 @@
         <v>123297960</v>
       </c>
       <c r="B70" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8489,10 +8489,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123402533</v>
+        <v>123402528</v>
       </c>
       <c r="B71" t="n">
-        <v>58168</v>
+        <v>57861</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8505,16 +8505,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8609,10 +8609,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123402528</v>
+        <v>123402533</v>
       </c>
       <c r="B72" t="n">
-        <v>57860</v>
+        <v>58169</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8625,16 +8625,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8727,6 +8727,342 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>123948803</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91400</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>654729</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6566075</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>123949266</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5196</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>654645</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6566069</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>123948552</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91010</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>654811</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6566075</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -8841,10 +8841,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948803</v>
+        <v>123948552</v>
       </c>
       <c r="B74" t="n">
-        <v>91422</v>
+        <v>91032</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8853,25 +8853,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>654729</v>
+        <v>654811</v>
       </c>
       <c r="R74" t="n">
         <v>6566075</v>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8953,10 +8953,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948552</v>
+        <v>123948803</v>
       </c>
       <c r="B75" t="n">
-        <v>91032</v>
+        <v>91422</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8965,25 +8965,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>654811</v>
+        <v>654729</v>
       </c>
       <c r="R75" t="n">
         <v>6566075</v>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -8729,10 +8729,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123949266</v>
+        <v>123948552</v>
       </c>
       <c r="B73" t="n">
-        <v>5196</v>
+        <v>91032</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8741,25 +8741,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>105930</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8769,10 +8769,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>654645</v>
+        <v>654811</v>
       </c>
       <c r="R73" t="n">
-        <v>6566069</v>
+        <v>6566075</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8841,10 +8841,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948552</v>
+        <v>123948803</v>
       </c>
       <c r="B74" t="n">
-        <v>91032</v>
+        <v>91422</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8853,25 +8853,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>654811</v>
+        <v>654729</v>
       </c>
       <c r="R74" t="n">
         <v>6566075</v>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8953,10 +8953,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948803</v>
+        <v>123949266</v>
       </c>
       <c r="B75" t="n">
-        <v>91422</v>
+        <v>5196</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8969,21 +8969,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5420</v>
+        <v>105930</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>654729</v>
+        <v>654645</v>
       </c>
       <c r="R75" t="n">
-        <v>6566075</v>
+        <v>6566069</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -8841,10 +8841,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948803</v>
+        <v>123949266</v>
       </c>
       <c r="B74" t="n">
-        <v>91422</v>
+        <v>5196</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8857,21 +8857,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5420</v>
+        <v>105930</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8881,10 +8881,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>654729</v>
+        <v>654645</v>
       </c>
       <c r="R74" t="n">
-        <v>6566075</v>
+        <v>6566069</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8953,10 +8953,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123949266</v>
+        <v>123948803</v>
       </c>
       <c r="B75" t="n">
-        <v>5196</v>
+        <v>91422</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8969,21 +8969,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>105930</v>
+        <v>5420</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>654645</v>
+        <v>654729</v>
       </c>
       <c r="R75" t="n">
-        <v>6566069</v>
+        <v>6566075</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -8841,10 +8841,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123949266</v>
+        <v>123948803</v>
       </c>
       <c r="B74" t="n">
-        <v>5196</v>
+        <v>91422</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8857,21 +8857,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>105930</v>
+        <v>5420</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8881,10 +8881,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>654645</v>
+        <v>654729</v>
       </c>
       <c r="R74" t="n">
-        <v>6566069</v>
+        <v>6566075</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8953,10 +8953,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123948803</v>
+        <v>123949266</v>
       </c>
       <c r="B75" t="n">
-        <v>91422</v>
+        <v>5196</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8969,21 +8969,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5420</v>
+        <v>105930</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>654729</v>
+        <v>654645</v>
       </c>
       <c r="R75" t="n">
-        <v>6566075</v>
+        <v>6566069</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9063,6 +9063,118 @@
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128207955</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>654700</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6566085</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9175,6 +9175,658 @@
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128269651</v>
+      </c>
+      <c r="B77" t="n">
+        <v>58042</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>654597</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6566218</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128270496</v>
+      </c>
+      <c r="B78" t="n">
+        <v>92654</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>655075</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6566034</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128269471</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91984</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>654653</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6566069</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128270101</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>654849</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6566121</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128269483</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91984</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>654643</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6566070</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128270392</v>
+      </c>
+      <c r="B82" t="n">
+        <v>105508</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>655033</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6566120</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9068,7 +9068,7 @@
         <v>128207955</v>
       </c>
       <c r="B76" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>128269651</v>
       </c>
       <c r="B77" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>128270496</v>
       </c>
       <c r="B78" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>128269471</v>
       </c>
       <c r="B79" t="n">
-        <v>91984</v>
+        <v>91992</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>128270101</v>
       </c>
       <c r="B80" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>128269483</v>
       </c>
       <c r="B81" t="n">
-        <v>91984</v>
+        <v>91992</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>128270392</v>
       </c>
       <c r="B82" t="n">
-        <v>105508</v>
+        <v>105516</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9068,7 +9068,7 @@
         <v>128207955</v>
       </c>
       <c r="B76" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>128269651</v>
       </c>
       <c r="B77" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>128270496</v>
       </c>
       <c r="B78" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>128269471</v>
       </c>
       <c r="B79" t="n">
-        <v>91992</v>
+        <v>92084</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>128270101</v>
       </c>
       <c r="B80" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>128269483</v>
       </c>
       <c r="B81" t="n">
-        <v>91992</v>
+        <v>92084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>128270392</v>
       </c>
       <c r="B82" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9826,6 +9826,225 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128540646</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>654823</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6565946</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128540550</v>
+      </c>
+      <c r="B84" t="n">
+        <v>90987</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>654727</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6565989</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9832,7 +9832,7 @@
         <v>128540646</v>
       </c>
       <c r="B83" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>128540550</v>
       </c>
       <c r="B84" t="n">
-        <v>90987</v>
+        <v>90993</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9068,7 +9068,7 @@
         <v>128207955</v>
       </c>
       <c r="B76" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>128269651</v>
       </c>
       <c r="B77" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>128270496</v>
       </c>
       <c r="B78" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>128269471</v>
       </c>
       <c r="B79" t="n">
-        <v>92084</v>
+        <v>92096</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>128270101</v>
       </c>
       <c r="B80" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>128269483</v>
       </c>
       <c r="B81" t="n">
-        <v>92084</v>
+        <v>92096</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>128270392</v>
       </c>
       <c r="B82" t="n">
-        <v>105609</v>
+        <v>105630</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>128540550</v>
       </c>
       <c r="B84" t="n">
-        <v>90993</v>
+        <v>90999</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9292,7 +9292,7 @@
         <v>128270496</v>
       </c>
       <c r="B78" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>128269471</v>
       </c>
       <c r="B79" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>128269483</v>
       </c>
       <c r="B81" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>128270392</v>
       </c>
       <c r="B82" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>128540550</v>
       </c>
       <c r="B84" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9725,7 +9725,7 @@
         <v>128270392</v>
       </c>
       <c r="B82" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9292,7 +9292,7 @@
         <v>128270496</v>
       </c>
       <c r="B78" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>128269471</v>
       </c>
       <c r="B79" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>128269483</v>
       </c>
       <c r="B81" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>128270392</v>
       </c>
       <c r="B82" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>128540550</v>
       </c>
       <c r="B84" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9832,7 +9832,7 @@
         <v>128540646</v>
       </c>
       <c r="B83" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>128540550</v>
       </c>
       <c r="B84" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9068,7 +9068,7 @@
         <v>128207955</v>
       </c>
       <c r="B76" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>128269651</v>
       </c>
       <c r="B77" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>128270496</v>
       </c>
       <c r="B78" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>128269471</v>
       </c>
       <c r="B79" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>128270101</v>
       </c>
       <c r="B80" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>128269483</v>
       </c>
       <c r="B81" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>128270392</v>
       </c>
       <c r="B82" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9944,7 +9944,7 @@
         <v>128540550</v>
       </c>
       <c r="B84" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9292,7 +9292,7 @@
         <v>128270496</v>
       </c>
       <c r="B78" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>128269471</v>
       </c>
       <c r="B79" t="n">
-        <v>92126</v>
+        <v>92136</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>128269483</v>
       </c>
       <c r="B81" t="n">
-        <v>92126</v>
+        <v>92136</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>128270392</v>
       </c>
       <c r="B82" t="n">
-        <v>105682</v>
+        <v>105695</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>128540550</v>
       </c>
       <c r="B84" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9832,7 +9832,7 @@
         <v>128540646</v>
       </c>
       <c r="B83" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>128540550</v>
       </c>
       <c r="B84" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9832,7 +9832,7 @@
         <v>128540646</v>
       </c>
       <c r="B83" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>128540550</v>
       </c>
       <c r="B84" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9944,7 +9944,7 @@
         <v>128540550</v>
       </c>
       <c r="B84" t="n">
-        <v>91050</v>
+        <v>91055</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -9944,7 +9944,7 @@
         <v>128540550</v>
       </c>
       <c r="B84" t="n">
-        <v>91055</v>
+        <v>91061</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10046,6 +10046,121 @@
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>130098812</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Ersboda naturskog, Srm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>654999</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6566083</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Martin Resare</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Martin Resare</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -10051,7 +10051,7 @@
         <v>130098812</v>
       </c>
       <c r="B85" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10161,6 +10161,130 @@
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>130918991</v>
+      </c>
+      <c r="B86" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Ersboda naturskog, Srm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>654999</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6566083</v>
+      </c>
+      <c r="S86" t="n">
+        <v>25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På matning</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Martin Resare</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Martin Resare</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105340873</v>
+        <v>119576631</v>
       </c>
       <c r="B2" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2008</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda, Ersboda, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655106.8500910378</v>
+        <v>654702</v>
       </c>
       <c r="R2" t="n">
-        <v>6566038.144157222</v>
+        <v>6566208</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-12-25</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-12-25</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,51 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111613688</v>
+        <v>115194266</v>
       </c>
       <c r="B3" t="n">
-        <v>90018</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655106.8500910378</v>
+        <v>654960</v>
       </c>
       <c r="R3" t="n">
-        <v>6566038.144157222</v>
+        <v>6566125</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111613637</v>
+        <v>112822677</v>
       </c>
       <c r="B4" t="n">
-        <v>88966</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5754</v>
+        <v>1106</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655106.8500910378</v>
+        <v>654976</v>
       </c>
       <c r="R4" t="n">
-        <v>6566038.144157222</v>
+        <v>6566126</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,22 +955,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,15 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112217458</v>
+        <v>113049220</v>
       </c>
       <c r="B5" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1008,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>1106</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,13 +1033,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654807</v>
+        <v>654984</v>
       </c>
       <c r="R5" t="n">
-        <v>6565995</v>
+        <v>6566139</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1063,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,15 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112217490</v>
+        <v>115779025</v>
       </c>
       <c r="B6" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,38 +1116,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>1106</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654692</v>
+        <v>654700</v>
       </c>
       <c r="R6" t="n">
-        <v>6566084</v>
+        <v>6566003</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,22 +1170,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,27 +1195,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112217496</v>
+        <v>115779026</v>
       </c>
       <c r="B7" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,38 +1218,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>1106</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654836</v>
+        <v>655023</v>
       </c>
       <c r="R7" t="n">
-        <v>6566058</v>
+        <v>6566023</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1272,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,66 +1297,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112822677</v>
+        <v>115779031</v>
       </c>
       <c r="B8" t="n">
-        <v>90134</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654976</v>
+        <v>654668</v>
       </c>
       <c r="R8" t="n">
-        <v>6566126</v>
+        <v>6566145</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,22 +1374,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,66 +1399,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113049220</v>
+        <v>116177054</v>
       </c>
       <c r="B9" t="n">
-        <v>90241</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654985</v>
+        <v>654826</v>
       </c>
       <c r="R9" t="n">
-        <v>6566139</v>
+        <v>6566130</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,22 +1476,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,51 +1518,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210471</v>
+        <v>116177264</v>
       </c>
       <c r="B10" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda, Ersboda, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654929</v>
+        <v>654668</v>
       </c>
       <c r="R10" t="n">
-        <v>6566093</v>
+        <v>6566152</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1654,22 +1583,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,59 +1625,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115116034</v>
+        <v>111613688</v>
       </c>
       <c r="B11" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654869</v>
+        <v>655106</v>
       </c>
       <c r="R11" t="n">
-        <v>6566029</v>
+        <v>6566039</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1775,22 +1691,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,15 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115118627</v>
+        <v>105340873</v>
       </c>
       <c r="B12" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,37 +1744,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>2008</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654819</v>
+        <v>655106</v>
       </c>
       <c r="R12" t="n">
-        <v>6566089</v>
+        <v>6566039</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,22 +1803,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2022-12-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2022-12-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,7 +1827,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1933,56 +1845,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115118236</v>
+        <v>115398960</v>
       </c>
       <c r="B13" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654901</v>
+        <v>654807</v>
       </c>
       <c r="R13" t="n">
-        <v>6565999</v>
+        <v>6565995</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2006,22 +1910,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,7 +1934,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2049,15 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115116043</v>
+        <v>122788085</v>
       </c>
       <c r="B14" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,37 +1963,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654886</v>
+        <v>654853</v>
       </c>
       <c r="R14" t="n">
-        <v>6565998</v>
+        <v>6565997</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2119,22 +2017,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,15 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115131856</v>
+        <v>122765519</v>
       </c>
       <c r="B15" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,37 +2070,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654899</v>
+        <v>654844</v>
       </c>
       <c r="R15" t="n">
-        <v>6566061</v>
+        <v>6566122</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2231,22 +2124,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,15 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115137071</v>
+        <v>119535164</v>
       </c>
       <c r="B16" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,37 +2177,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>4363</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654915</v>
+        <v>654974</v>
       </c>
       <c r="R16" t="n">
-        <v>6566062</v>
+        <v>6565955</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2343,22 +2231,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,53 +2273,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115137123</v>
+        <v>122788048</v>
       </c>
       <c r="B17" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654884</v>
+        <v>654899</v>
       </c>
       <c r="R17" t="n">
-        <v>6566030</v>
+        <v>6565949</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,22 +2338,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,53 +2380,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115137051</v>
+        <v>128270496</v>
       </c>
       <c r="B18" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654899</v>
+        <v>655075</v>
       </c>
       <c r="R18" t="n">
-        <v>6566061</v>
+        <v>6566034</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2567,22 +2445,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,55 +2487,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115154877</v>
+        <v>115696785</v>
       </c>
       <c r="B19" t="n">
-        <v>57156</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100001</v>
+        <v>5420</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654646</v>
+        <v>654575</v>
       </c>
       <c r="R19" t="n">
-        <v>6566051</v>
+        <v>6566177</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2684,27 +2555,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Slakt plats där större hackspett nyligen ätits upp</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2713,6 +2579,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2731,15 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115153965</v>
+        <v>119577528</v>
       </c>
       <c r="B20" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,37 +2609,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654849</v>
+        <v>654725</v>
       </c>
       <c r="R20" t="n">
-        <v>6566121</v>
+        <v>6566054</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2801,22 +2663,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2843,58 +2705,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115154179</v>
+        <v>123948803</v>
       </c>
       <c r="B21" t="n">
-        <v>57156</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100001</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654849</v>
+        <v>654729</v>
       </c>
       <c r="R21" t="n">
-        <v>6566121</v>
+        <v>6566075</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2918,27 +2770,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Slakt plats där nötskrika nyligen ätits upp</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,50 +2812,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115151777</v>
+        <v>115116034</v>
       </c>
       <c r="B22" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654980</v>
+        <v>654869</v>
       </c>
       <c r="R22" t="n">
-        <v>6566033</v>
+        <v>6566029</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3035,22 +2886,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3077,50 +2928,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115152796</v>
+        <v>115697091</v>
       </c>
       <c r="B23" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Salem, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654898</v>
+        <v>654737</v>
       </c>
       <c r="R23" t="n">
-        <v>6566092</v>
+        <v>6566147</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3147,22 +2993,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3189,15 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115189650</v>
+        <v>115779034</v>
       </c>
       <c r="B24" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3205,39 +3046,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654842</v>
+        <v>654868</v>
       </c>
       <c r="R24" t="n">
-        <v>6565904</v>
+        <v>6566045</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3264,22 +3100,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3294,27 +3120,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115272740</v>
+        <v>122129248</v>
       </c>
       <c r="B25" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3322,51 +3143,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654692</v>
+        <v>654831</v>
       </c>
       <c r="R25" t="n">
-        <v>6566084</v>
+        <v>6566094</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3390,22 +3197,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3432,53 +3239,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115398960</v>
+        <v>122765657</v>
       </c>
       <c r="B26" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654807</v>
+        <v>654811</v>
       </c>
       <c r="R26" t="n">
-        <v>6565995</v>
+        <v>6566078</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3502,22 +3304,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,15 +3346,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115399448</v>
+        <v>123948552</v>
       </c>
       <c r="B27" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,42 +3357,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654929</v>
+        <v>654811</v>
       </c>
       <c r="R27" t="n">
-        <v>6566093</v>
+        <v>6566075</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3619,22 +3411,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,58 +3453,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115398869</v>
+        <v>115131856</v>
       </c>
       <c r="B28" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654836</v>
+        <v>654899</v>
       </c>
       <c r="R28" t="n">
-        <v>6566058</v>
+        <v>6566061</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3736,22 +3518,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3778,55 +3560,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115457602</v>
+        <v>115779027</v>
       </c>
       <c r="B29" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654849</v>
+        <v>654859</v>
       </c>
       <c r="R29" t="n">
-        <v>6566121</v>
+        <v>6566085</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3853,22 +3625,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>08:11</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>08:11</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3883,65 +3650,63 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115629739</v>
+        <v>128184801</v>
       </c>
       <c r="B30" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>5741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655106</v>
+        <v>655004</v>
       </c>
       <c r="R30" t="n">
-        <v>6566039</v>
+        <v>6566168</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3965,22 +3730,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3989,6 +3754,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4007,50 +3773,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115629634</v>
+        <v>128540550</v>
       </c>
       <c r="B31" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106554</v>
+        <v>5747</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ersboda , Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654947</v>
+        <v>654727</v>
       </c>
       <c r="R31" t="n">
-        <v>6566063</v>
+        <v>6565989</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4077,22 +3838,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4119,40 +3880,36 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115629718</v>
+        <v>111613637</v>
       </c>
       <c r="B32" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>5754</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ersboda , Srm</t>
@@ -4189,22 +3946,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4231,58 +3988,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115629727</v>
+        <v>128152798</v>
       </c>
       <c r="B33" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ersboda, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654577</v>
+        <v>655161</v>
       </c>
       <c r="R33" t="n">
-        <v>6566106</v>
+        <v>6565982</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4306,22 +4053,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4330,7 +4077,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4349,15 +4095,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115697091</v>
+        <v>112217458</v>
       </c>
       <c r="B34" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4365,37 +4106,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Salem, Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654737</v>
+        <v>654807</v>
       </c>
       <c r="R34" t="n">
-        <v>6566147</v>
+        <v>6565995</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4419,22 +4161,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4461,58 +4203,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115629681</v>
+        <v>112217490</v>
       </c>
       <c r="B35" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ersboda, Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654581</v>
+        <v>654692</v>
       </c>
       <c r="R35" t="n">
-        <v>6566102</v>
+        <v>6566084</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4536,22 +4269,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4560,7 +4293,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4579,56 +4311,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115696785</v>
+        <v>112217496</v>
       </c>
       <c r="B36" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ersboda, Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654575</v>
+        <v>654836</v>
       </c>
       <c r="R36" t="n">
-        <v>6566177</v>
+        <v>6566058</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4652,22 +4377,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4676,7 +4401,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4695,15 +4419,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115629663</v>
+        <v>128269471</v>
       </c>
       <c r="B37" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4711,42 +4430,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>6031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ersboda, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654571</v>
+        <v>654653</v>
       </c>
       <c r="R37" t="n">
-        <v>6566114</v>
+        <v>6566069</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4770,22 +4484,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4794,7 +4508,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4813,15 +4526,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115779042</v>
+        <v>128269483</v>
       </c>
       <c r="B38" t="n">
-        <v>4769</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4829,37 +4537,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102306</v>
+        <v>6031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654828</v>
+        <v>654643</v>
       </c>
       <c r="R38" t="n">
-        <v>6566121</v>
+        <v>6566070</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4883,17 +4591,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>gnag</t>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4908,62 +4621,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115779027</v>
+        <v>115118236</v>
       </c>
       <c r="B39" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654859</v>
+        <v>654901</v>
       </c>
       <c r="R39" t="n">
-        <v>6566085</v>
+        <v>6565999</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4990,17 +4701,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5009,33 +4725,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115779031</v>
+        <v>115118627</v>
       </c>
       <c r="B40" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5043,34 +4755,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654668</v>
+        <v>654819</v>
       </c>
       <c r="R40" t="n">
-        <v>6566145</v>
+        <v>6566089</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5097,17 +4812,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5116,55 +4836,51 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115779026</v>
+        <v>115779028</v>
       </c>
       <c r="B41" t="n">
-        <v>90532</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1106</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5174,10 +4890,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655023</v>
+        <v>654823</v>
       </c>
       <c r="R41" t="n">
-        <v>6566023</v>
+        <v>6566106</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5210,11 +4926,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5241,15 +4952,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115779037</v>
+        <v>115154179</v>
       </c>
       <c r="B42" t="n">
-        <v>5479</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5257,34 +4963,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101410</v>
+        <v>100001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654847</v>
+        <v>654849</v>
       </c>
       <c r="R42" t="n">
-        <v>6565867</v>
+        <v>6566121</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5311,17 +5022,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>gnag</t>
+          <t>Slakt plats där nötskrika nyligen ätits upp</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5336,27 +5057,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115779041</v>
+        <v>115154877</v>
       </c>
       <c r="B43" t="n">
-        <v>5348</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5364,34 +5080,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101728</v>
+        <v>100001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654885</v>
+        <v>654646</v>
       </c>
       <c r="R43" t="n">
-        <v>6565841</v>
+        <v>6566051</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5418,17 +5139,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>gnag</t>
+          <t>Slakt plats där större hackspett nyligen ätits upp</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5443,27 +5174,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>115779034</v>
+        <v>122788791</v>
       </c>
       <c r="B44" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,37 +5197,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>100001</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654868</v>
+        <v>654687</v>
       </c>
       <c r="R44" t="n">
-        <v>6566045</v>
+        <v>6566048</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5525,12 +5256,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5545,27 +5286,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>115779028</v>
+        <v>129380015</v>
       </c>
       <c r="B45" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5573,37 +5309,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654823</v>
+        <v>654958</v>
       </c>
       <c r="R45" t="n">
-        <v>6566106</v>
+        <v>6566141</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5627,12 +5368,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5647,62 +5398,62 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>115779025</v>
+        <v>115189650</v>
       </c>
       <c r="B46" t="n">
-        <v>90532</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1106</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654700</v>
+        <v>654842</v>
       </c>
       <c r="R46" t="n">
-        <v>6566003</v>
+        <v>6565904</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5729,17 +5480,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5754,27 +5510,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>115779047</v>
+        <v>115272740</v>
       </c>
       <c r="B47" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5782,37 +5533,51 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654992</v>
+        <v>654692</v>
       </c>
       <c r="R47" t="n">
-        <v>6566057</v>
+        <v>6566084</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5836,17 +5601,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>gnag</t>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5861,27 +5631,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>116176686</v>
+        <v>115399448</v>
       </c>
       <c r="B48" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5889,16 +5654,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5909,19 +5674,19 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ersboda  (Ersboda ), Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654908</v>
+        <v>654929</v>
       </c>
       <c r="R48" t="n">
-        <v>6566102</v>
+        <v>6566093</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5948,22 +5713,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5990,53 +5755,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>116177264</v>
+        <v>116207774</v>
       </c>
       <c r="B49" t="n">
-        <v>90417</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ersboda (Ersboda), Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654668</v>
+        <v>654777</v>
       </c>
       <c r="R49" t="n">
-        <v>6566152</v>
+        <v>6565992</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6060,22 +5825,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6102,53 +5867,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>116177054</v>
+        <v>119535239</v>
       </c>
       <c r="B50" t="n">
-        <v>90417</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Ersboda Salem (Ersboda Salem), Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654826</v>
+        <v>654948</v>
       </c>
       <c r="R50" t="n">
-        <v>6566130</v>
+        <v>6566038</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6172,22 +5937,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6214,58 +5979,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>116208534</v>
+        <v>121734801</v>
       </c>
       <c r="B51" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Salem (Salem), Srm</t>
+          <t>Ersboda, Ersboda, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654670</v>
+        <v>654665</v>
       </c>
       <c r="R51" t="n">
-        <v>6566054</v>
+        <v>6566198</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6289,22 +6049,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6331,19 +6091,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>116207774</v>
+        <v>122128440</v>
       </c>
       <c r="B52" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6372,14 +6127,14 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ersboda  (Ersboda ), Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654777</v>
+        <v>654898</v>
       </c>
       <c r="R52" t="n">
-        <v>6565992</v>
+        <v>6565826</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6406,22 +6161,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>09:43</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>09:43</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6448,19 +6193,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119535239</v>
+        <v>122129293</v>
       </c>
       <c r="B53" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6493,13 +6233,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654948</v>
+        <v>654792</v>
       </c>
       <c r="R53" t="n">
-        <v>6566038</v>
+        <v>6566105</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6523,22 +6263,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6565,15 +6305,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119577528</v>
+        <v>122765355</v>
       </c>
       <c r="B54" t="n">
-        <v>90966</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6581,37 +6316,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654725</v>
+        <v>654953</v>
       </c>
       <c r="R54" t="n">
-        <v>6566054</v>
+        <v>6566038</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6635,22 +6375,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6677,53 +6417,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119576631</v>
+        <v>128270101</v>
       </c>
       <c r="B55" t="n">
-        <v>91860</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>788</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ersboda, Ersboda, Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654702</v>
+        <v>654849</v>
       </c>
       <c r="R55" t="n">
-        <v>6566208</v>
+        <v>6566121</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6747,22 +6487,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6789,19 +6529,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121734801</v>
+        <v>128540646</v>
       </c>
       <c r="B56" t="n">
-        <v>57388</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6825,19 +6560,19 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ersboda, Ersboda, Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654665</v>
+        <v>654823</v>
       </c>
       <c r="R56" t="n">
-        <v>6566198</v>
+        <v>6565946</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6864,22 +6599,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6906,53 +6641,56 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122129248</v>
+        <v>130098812</v>
       </c>
       <c r="B57" t="n">
-        <v>90859</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda naturskog, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654831</v>
+        <v>654999</v>
       </c>
       <c r="R57" t="n">
-        <v>6566094</v>
+        <v>6566083</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6976,22 +6714,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7006,31 +6744,26 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Resare</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Resare</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122128440</v>
+        <v>131069884</v>
       </c>
       <c r="B58" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -7054,19 +6787,19 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654898</v>
+        <v>654643</v>
       </c>
       <c r="R58" t="n">
-        <v>6565826</v>
+        <v>6565989</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7093,12 +6826,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7118,26 +6861,21 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Jan-Erik Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122129293</v>
+        <v>131407030</v>
       </c>
       <c r="B59" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -7161,7 +6899,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7170,10 +6908,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654792</v>
+        <v>654627</v>
       </c>
       <c r="R59" t="n">
-        <v>6566105</v>
+        <v>6566003</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7200,22 +6938,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7242,15 +6980,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122734105</v>
+        <v>113210471</v>
       </c>
       <c r="B60" t="n">
-        <v>43825</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7258,37 +6991,38 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>101735</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>655010</v>
+        <v>654929</v>
       </c>
       <c r="R60" t="n">
-        <v>6566065</v>
+        <v>6566093</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7312,22 +7046,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7354,53 +7088,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122765657</v>
+        <v>115137051</v>
       </c>
       <c r="B61" t="n">
-        <v>90983</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654811</v>
+        <v>654899</v>
       </c>
       <c r="R61" t="n">
-        <v>6566078</v>
+        <v>6566061</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7424,22 +7153,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7466,15 +7195,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122765305</v>
+        <v>115137071</v>
       </c>
       <c r="B62" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7502,17 +7226,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654978</v>
+        <v>654915</v>
       </c>
       <c r="R62" t="n">
-        <v>6565979</v>
+        <v>6566062</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7536,22 +7260,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7578,15 +7302,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122765368</v>
+        <v>115151777</v>
       </c>
       <c r="B63" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7614,17 +7333,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654946</v>
+        <v>654980</v>
       </c>
       <c r="R63" t="n">
-        <v>6566044</v>
+        <v>6566033</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7648,22 +7367,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7690,58 +7409,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122765355</v>
+        <v>115152796</v>
       </c>
       <c r="B64" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654953</v>
+        <v>654898</v>
       </c>
       <c r="R64" t="n">
-        <v>6566038</v>
+        <v>6566092</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7765,22 +7474,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7807,15 +7516,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122788386</v>
+        <v>115153965</v>
       </c>
       <c r="B65" t="n">
-        <v>97333</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7823,37 +7527,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654629</v>
+        <v>654849</v>
       </c>
       <c r="R65" t="n">
-        <v>6566054</v>
+        <v>6566121</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7877,22 +7581,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7919,15 +7623,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122788048</v>
+        <v>115629727</v>
       </c>
       <c r="B66" t="n">
-        <v>92247</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7935,37 +7634,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654899</v>
+        <v>654577</v>
       </c>
       <c r="R66" t="n">
-        <v>6565949</v>
+        <v>6566106</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7989,22 +7693,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8013,6 +7717,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8031,58 +7736,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122788791</v>
+        <v>115629739</v>
       </c>
       <c r="B67" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100001</v>
+        <v>100526</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654687</v>
+        <v>655106</v>
       </c>
       <c r="R67" t="n">
-        <v>6566048</v>
+        <v>6566039</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8106,22 +7801,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8148,15 +7843,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122765519</v>
+        <v>115779047</v>
       </c>
       <c r="B68" t="n">
-        <v>94780</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8164,37 +7854,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2809</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654844</v>
+        <v>654992</v>
       </c>
       <c r="R68" t="n">
-        <v>6566122</v>
+        <v>6566057</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8218,22 +7908,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8248,27 +7933,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122788085</v>
+        <v>122765305</v>
       </c>
       <c r="B69" t="n">
-        <v>95150</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8276,21 +7956,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8300,10 +7980,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654853</v>
+        <v>654978</v>
       </c>
       <c r="R69" t="n">
-        <v>6565997</v>
+        <v>6565979</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8330,22 +8010,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8372,55 +8052,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123297960</v>
+        <v>122765368</v>
       </c>
       <c r="B70" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ersboda , Rönninge, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>655037</v>
+        <v>654946</v>
       </c>
       <c r="R70" t="n">
-        <v>6565990</v>
+        <v>6566044</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8447,22 +8117,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8489,58 +8159,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123402528</v>
+        <v>115779037</v>
       </c>
       <c r="B71" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103015</v>
+        <v>101410</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ersboda naturskog, Srm</t>
+          <t>Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>654999</v>
+        <v>654847</v>
       </c>
       <c r="R71" t="n">
-        <v>6566083</v>
+        <v>6565867</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8567,22 +8224,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8597,27 +8249,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Resare</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Resare</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123402533</v>
+        <v>122734105</v>
       </c>
       <c r="B72" t="n">
-        <v>58191</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8625,45 +8272,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103044</v>
+        <v>101735</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ersboda naturskog, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>654999</v>
+        <v>655010</v>
       </c>
       <c r="R72" t="n">
-        <v>6566083</v>
+        <v>6566065</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8687,22 +8326,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8717,65 +8356,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Resare</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Resare</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123948552</v>
+        <v>115779042</v>
       </c>
       <c r="B73" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>654811</v>
+        <v>654828</v>
       </c>
       <c r="R73" t="n">
-        <v>6566075</v>
+        <v>6566121</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8799,22 +8433,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8829,27 +8458,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123948803</v>
+        <v>115709047</v>
       </c>
       <c r="B74" t="n">
-        <v>91422</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8857,37 +8481,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>654729</v>
+        <v>654890</v>
       </c>
       <c r="R74" t="n">
-        <v>6566075</v>
+        <v>6565810</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8911,22 +8540,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8953,15 +8582,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123949266</v>
+        <v>116176686</v>
       </c>
       <c r="B75" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8969,16 +8593,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8987,19 +8611,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>654645</v>
+        <v>654908</v>
       </c>
       <c r="R75" t="n">
-        <v>6566069</v>
+        <v>6566102</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9023,22 +8652,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9065,53 +8694,56 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128207955</v>
+        <v>123402528</v>
       </c>
       <c r="B76" t="n">
-        <v>57876</v>
+        <v>58327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda naturskog, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>654700</v>
+        <v>654999</v>
       </c>
       <c r="R76" t="n">
-        <v>6566085</v>
+        <v>6566083</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9135,22 +8767,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9165,22 +8797,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Resare</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Resare</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128269651</v>
+        <v>128102394</v>
       </c>
       <c r="B77" t="n">
-        <v>58086</v>
+        <v>58327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9217,10 +8849,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>654597</v>
+        <v>654902</v>
       </c>
       <c r="R77" t="n">
-        <v>6566218</v>
+        <v>6566175</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9247,22 +8879,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9289,10 +8921,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128270496</v>
+        <v>128269651</v>
       </c>
       <c r="B78" t="n">
-        <v>92806</v>
+        <v>58327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9300,34 +8932,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4366</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>655075</v>
+        <v>654597</v>
       </c>
       <c r="R78" t="n">
-        <v>6566034</v>
+        <v>6566218</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9359,7 +8996,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9369,7 +9006,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9396,10 +9033,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128269471</v>
+        <v>128270336</v>
       </c>
       <c r="B79" t="n">
-        <v>92136</v>
+        <v>58327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9407,21 +9044,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6031</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9431,10 +9068,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>654653</v>
+        <v>654965</v>
       </c>
       <c r="R79" t="n">
-        <v>6566069</v>
+        <v>6566133</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9466,7 +9103,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9476,7 +9113,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9503,10 +9140,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128270101</v>
+        <v>115398869</v>
       </c>
       <c r="B80" t="n">
-        <v>57713</v>
+        <v>58114</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9514,21 +9151,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9543,13 +9180,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>654849</v>
+        <v>654836</v>
       </c>
       <c r="R80" t="n">
-        <v>6566121</v>
+        <v>6566058</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9573,22 +9210,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9615,48 +9252,53 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128269483</v>
+        <v>115457602</v>
       </c>
       <c r="B81" t="n">
-        <v>92136</v>
+        <v>58114</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6031</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>654643</v>
+        <v>654849</v>
       </c>
       <c r="R81" t="n">
-        <v>6566070</v>
+        <v>6566121</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9680,22 +9322,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9722,48 +9364,53 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128270392</v>
+        <v>116208534</v>
       </c>
       <c r="B82" t="n">
-        <v>105695</v>
+        <v>58114</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Salem, Salem, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655033</v>
+        <v>654670</v>
       </c>
       <c r="R82" t="n">
-        <v>6566120</v>
+        <v>6566054</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9787,22 +9434,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9829,10 +9476,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128540646</v>
+        <v>122252411</v>
       </c>
       <c r="B83" t="n">
-        <v>57720</v>
+        <v>58114</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9840,21 +9487,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9865,14 +9512,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Ersboda Salem, Ersboda Salem, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>654823</v>
+        <v>654974</v>
       </c>
       <c r="R83" t="n">
-        <v>6565946</v>
+        <v>6566146</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9899,22 +9546,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9941,45 +9588,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128540550</v>
+        <v>123297960</v>
       </c>
       <c r="B84" t="n">
-        <v>91061</v>
+        <v>58114</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5747</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda , Rönninge, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>654727</v>
+        <v>655037</v>
       </c>
       <c r="R84" t="n">
-        <v>6565989</v>
+        <v>6565990</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10006,22 +9658,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10048,10 +9700,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130098812</v>
+        <v>127044031</v>
       </c>
       <c r="B85" t="n">
-        <v>57823</v>
+        <v>58114</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10059,45 +9711,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ersboda naturskog, Srm</t>
+          <t>Ersboda Salem, Ersboda Salem, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654999</v>
+        <v>654917</v>
       </c>
       <c r="R85" t="n">
-        <v>6566083</v>
+        <v>6565799</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10121,22 +9770,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10151,22 +9800,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Resare</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Resare</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130918991</v>
+        <v>128102375</v>
       </c>
       <c r="B86" t="n">
-        <v>58043</v>
+        <v>58114</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10191,32 +9840,25 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ersboda naturskog, Srm</t>
+          <t>Ersboda , Ersboda , Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654999</v>
+        <v>654902</v>
       </c>
       <c r="R86" t="n">
-        <v>6566083</v>
+        <v>6566175</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10240,27 +9882,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På matning</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10275,22 +9912,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Resare</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Resare</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131069884</v>
+        <v>128207955</v>
       </c>
       <c r="B87" t="n">
-        <v>57885</v>
+        <v>58114</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10298,27 +9935,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10327,10 +9964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>654643</v>
+        <v>654700</v>
       </c>
       <c r="R87" t="n">
-        <v>6565989</v>
+        <v>6566085</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10357,22 +9994,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10392,17 +10029,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Jan-Erik Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131407030</v>
+        <v>130918991</v>
       </c>
       <c r="B88" t="n">
-        <v>57904</v>
+        <v>58114</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10410,42 +10047,49 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ersboda , Ersboda , Srm</t>
+          <t>Ersboda naturskog, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>654627</v>
+        <v>654999</v>
       </c>
       <c r="R88" t="n">
-        <v>6566003</v>
+        <v>6566083</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10469,22 +10113,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På matning</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10499,15 +10148,1212 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Resare</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Resare</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>123402533</v>
+      </c>
+      <c r="B89" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Ersboda naturskog, Srm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>654999</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6566083</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Martin Resare</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Martin Resare</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>115629681</v>
+      </c>
+      <c r="B90" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Ersboda, Srm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>654581</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6566102</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>115629718</v>
+      </c>
+      <c r="B91" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>655106</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6566039</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>123949266</v>
+      </c>
+      <c r="B92" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>654645</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6566069</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>115137123</v>
+      </c>
+      <c r="B93" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>654884</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6566030</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>115116043</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>654886</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6565998</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>115629634</v>
+      </c>
+      <c r="B95" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>654947</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6566063</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>115629663</v>
+      </c>
+      <c r="B96" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Ersboda, Srm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>654571</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6566114</v>
+      </c>
+      <c r="S96" t="n">
+        <v>25</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128270392</v>
+      </c>
+      <c r="B97" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>655033</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6566120</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>115209432</v>
+      </c>
+      <c r="B98" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>654781</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6566242</v>
+      </c>
+      <c r="S98" t="n">
+        <v>25</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>122788386</v>
+      </c>
+      <c r="B99" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Ersboda , Ersboda , Srm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>654629</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6566054</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9538-2024 artfynd.xlsx
+++ b/artfynd/A 9538-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AZ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119576631</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115194266</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112822677</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113049220</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115779025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115779026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115779031</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116177054</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116177264</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1730,6 +1780,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111613688</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1842,6 +1897,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105340873</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1949,6 +2009,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115398960</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2056,6 +2121,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122788085</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2163,6 +2233,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122765519</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2270,6 +2345,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119535164</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2377,6 +2457,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122788048</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2484,6 +2569,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128270496</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2595,6 +2685,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115696785</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2702,6 +2797,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119577528</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2809,6 +2909,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123948803</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2925,6 +3030,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115116034</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3032,6 +3142,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115697091</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3129,6 +3244,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115779034</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3236,6 +3356,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122129248</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3343,6 +3468,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122765657</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3450,6 +3580,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123948552</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3557,6 +3692,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115131856</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3659,6 +3799,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115779027</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3770,6 +3915,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128184801</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3877,6 +4027,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128540550</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3985,6 +4140,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111613637</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4092,6 +4252,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128152798</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4200,6 +4365,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112217458</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4308,6 +4478,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112217490</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4416,6 +4591,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112217496</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4523,6 +4703,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128269471</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4630,6 +4815,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128269483</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4741,6 +4931,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115118236</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4852,6 +5047,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115118627</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4949,6 +5149,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115779028</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5066,6 +5271,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115154179</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5183,6 +5393,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115154877</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5295,6 +5510,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122788791</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5407,6 +5627,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129380015</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5519,6 +5744,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115189650</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5640,6 +5870,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115272740</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5752,6 +5987,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115399448</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5864,6 +6104,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116207774</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5976,6 +6221,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119535239</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6088,6 +6338,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121734801</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6190,6 +6445,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122128440</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6302,6 +6562,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122129293</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6414,6 +6679,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122765355</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6526,6 +6796,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128270101</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6638,6 +6913,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128540646</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6753,6 +7033,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130098812</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6865,6 +7150,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131069884</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6977,6 +7267,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131407030</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7085,6 +7380,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113210471</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7192,6 +7492,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115137051</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7299,6 +7604,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115137071</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7406,6 +7716,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115151777</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7513,6 +7828,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115152796</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7620,6 +7940,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115153965</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7733,6 +8058,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629727</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7840,6 +8170,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629739</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7942,6 +8277,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115779047</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8049,6 +8389,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122765305</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8156,6 +8501,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122765368</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8258,6 +8608,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115779037</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8365,6 +8720,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122734105</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8467,6 +8827,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115779042</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8579,6 +8944,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115709047</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8691,6 +9061,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116176686</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8806,6 +9181,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402528</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8918,6 +9298,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128102394</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9030,6 +9415,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128269651</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9137,6 +9527,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128270336</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9249,6 +9644,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115398869</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9361,6 +9761,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115457602</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9473,6 +9878,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116208534</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9585,6 +9995,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122252411</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9697,6 +10112,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123297960</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9809,6 +10229,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127044031</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9921,6 +10346,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128102375</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10033,6 +10463,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128207955</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10157,6 +10592,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130918991</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10272,6 +10712,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402533</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10385,6 +10830,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629681</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10492,6 +10942,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629718</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10599,6 +11054,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123949266</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10706,6 +11166,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115137123</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10813,6 +11278,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115116043</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10920,6 +11390,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629634</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11033,6 +11508,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629663</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11140,6 +11620,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128270392</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11247,6 +11732,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115209432</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11354,8 +11844,113 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122788386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>